--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>

--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -1795,9 +1795,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>src/App.js multiple</t>
+          <t>src/data/constants.js UI_COLORS + 75+ migrated call-sites</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
     <col width="53" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2952,17 +2952,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>pace bonus highlight</t>
+          <t>UI_COLORS.warning</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>One-off, not tokenised</t>
+          <t>Pace bonus highlight, accent emphasis (tokenised)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>src/App.js:118</t>
+          <t>src/data/constants.js</t>
         </is>
       </c>
     </row>
@@ -2974,17 +2974,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>success / beginner</t>
+          <t>UI_COLORS.success</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Green, used in multiple places</t>
+          <t>Green: positive, beginner, cardio (tokenised)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>src/App.js:23, 2884, 2995</t>
+          <t>src/data/constants.js</t>
         </is>
       </c>
     </row>
@@ -2996,39 +2996,39 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>error / advanced</t>
+          <t>UI_COLORS.danger</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Red, used in multiple places</t>
+          <t>Red: destructive, advanced, strength (tokenised)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>src/App.js:23, 2884, 2995</t>
+          <t>src/data/constants.js</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>#e05555</t>
+          <t>(removed)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>profile warning</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>One-off red variant</t>
+          <t>#e05555 consolidated into UI_COLORS.danger</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>src/App.js:7257</t>
+          <t>Was a near-duplicate of #e74c3c</t>
         </is>
       </c>
     </row>
@@ -3040,17 +3040,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>info text</t>
+          <t>UI_COLORS.info</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>One-off blue, not tokenised</t>
+          <t>Info text, message UI fallback (tokenised)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>src/App.js:3065</t>
+          <t>src/data/constants.js</t>
         </is>
       </c>
     </row>
@@ -3062,17 +3062,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>intermediate difficulty</t>
+          <t>UI_COLORS.intermediate</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Intermediate difficulty (tokenised)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>src/App.js:23</t>
+          <t>src/data/constants.js</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
@@ -3229,24 +3229,24 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Untokenised one-offs (#FFE87C, #2ecc71, #e74c3c, #e05555, #2980b9)</t>
+          <t>Inline one-off colors (#FFE87C, #2ecc71, #e74c3c, #e05555, #2980b9, #f1c40f) tokenised</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>src/App.js multiple</t>
+          <t>src/data/constants.js UI_COLORS</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Should be moved to a tokens module</t>
+          <t>Migrated 75+ inline JSX style hex strings to UI_COLORS.{warning, success, danger, info, intermediate}; #e05555 consolidated into danger</t>
         </is>
       </c>
     </row>

--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -1391,10 +1391,10 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="51" customWidth="1" min="2" max="2"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
-    <col width="49" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1425,46 +1425,46 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>reps schema is unstable across templates</t>
+          <t>reps and sets unified to string schema across all PLAN_TEMPLATES</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Numeric (reps:8) in ppl/cardio_week/monk_week/hiit_blast/full_body_day/morning_routine; quoted ('6-12','30s','45-60s','AMRAP') in dumbbell_8wk</t>
+          <t>Was: numeric (reps:8) in 6 templates; mixed (sets:3 numeric, reps:'6-12' string) in dumbbell_8wk</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>src/data/constants.js:1014-1083</t>
+          <t>src/data/constants.js PLAN_TEMPLATES</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Pick one schema (recommend strings) and migrate</t>
+          <t>All 244 sets/reps values now string-quoted; accommodates ranges (6-12), time (30s), special (AMRAP)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>No rest-period field in template exercise objects</t>
+          <t>restSec:null field added to every exercise object</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Schema gap — every template</t>
+          <t>Schema gap closed — 194 exercise entries updated</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Add restSec field</t>
+          <t>Field is null until plan UI exposes a rest-timer input</t>
         </is>
       </c>
     </row>
@@ -1521,8 +1521,8 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="61" customWidth="1" min="4" max="4"/>
+    <col width="63" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1773,19 +1773,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Reps schema standardisation in PLAN_TEMPLATES</t>
+          <t>Reps schema standardisation + restSec field in PLAN_TEMPLATES</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>src/data/constants.js:1014-1083</t>
+          <t>src/data/constants.js — 244 values quoted, 194 restSec:null fields added</t>
         </is>
       </c>
     </row>

--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -1522,7 +1522,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="63" customWidth="1" min="3" max="3"/>
-    <col width="74" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1751,19 +1751,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Masculine palette rollout to remaining tabs</t>
+          <t>Masculine palette rollout — CAT_ICON_COLORS + filter accents</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Profile/Trends/Friends/Leaderboard/Landing/PlanWizard</t>
+          <t>Profile/Library/PlanWizard now use UI_COLORS.accent for active states; xp.js fallback consolidated</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="73" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3251,14 +3251,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Two fallback colors (#B0A090 and #B0A898)</t>
+          <t>Two fallback colors consolidated to #B0A898</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3268,29 +3268,29 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Standardise to one</t>
+          <t>Both getMuscleColor and getTypeColor now fallback to silver palette token</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Masculine palette rollout incomplete</t>
+          <t>Masculine palette rollout — CAT_ICON_COLORS + filter accents</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Profile, Trends, Friends, Leaderboard, Landing, PlanWizard tabs</t>
+          <t>src/data/constants.js:15-17 + src/App.js + src/components/PlanWizard.js</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Verify per-tab application</t>
+          <t>CAT_ICON_COLORS now mirrors TYPE_COLORS masculine values; bright filter accents (#9b59b6, #3498db) migrated to UI_COLORS.accent (brand gold #c49428). Categorical chart colors and HR-zone palette intentionally preserved.</t>
         </is>
       </c>
     </row>

--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="75" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -982,46 +982,46 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>55 exercises with empty desc:""</t>
+          <t>Empty desc:"" populated with synthesised one-liners</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>src/data/exercises.js</t>
+          <t>src/data/exercises.js — 72 entries (55 originally empty + 17 with no usable sentence after trimming)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Populate or strip empty field</t>
+          <t>Format: '{Name} is a {category} exercise that targets {muscleGroup} using a {equipment}.'</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Truncated descriptions ending mid-word ('of', 'f')</t>
+          <t>Truncated descriptions trimmed to last full sentence</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>src/data/exercises.js (sample: atlas stone, sled push, EZ bar tricep extension)</t>
+          <t>src/data/exercises.js — 1,051 entries had imported source data cut mid-word</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Re-import or hand-edit affected entries</t>
+          <t>Heuristic trim back to last '.' / '!' / '?' followed by space; entries with no usable sentence were synthesised in pass 2</t>
         </is>
       </c>
     </row>
@@ -1685,19 +1685,19 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Populate 55 empty desc:'' exercises</t>
+          <t>Populate empty/truncated exercise descriptions</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>src/data/exercises.js</t>
+          <t>src/data/exercises.js — 72 empty entries synthesised + 1,051 truncated entries trimmed cleanly</t>
         </is>
       </c>
     </row>

--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -1521,7 +1521,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="63" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TODO</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Spacing/typography token system</t>
+          <t>Spacing/typography token system introduced + top values migrated</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Codebase-wide refactor</t>
+          <t>src/utils/tokens.js (new) — 329 highest-frequency values migrated; remaining stragglers tracked</t>
         </is>
       </c>
     </row>
@@ -3305,13 +3305,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="73" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3337,24 +3337,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20+ distinct font sizes (0.52, 0.55, 0.58, 0.6, 0.62, 0.63, 0.65, 0.68, 0.72, 0.78, 0.8, 0.82, 0.93rem...)</t>
+          <t>Token system introduced (FS scale)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Throughout app.css and inline styles</t>
+          <t>src/utils/tokens.js (new)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Consolidate to 8-10 tokens</t>
+          <t>8-step rem-based font-size scale (xxs→xxl). Top 3 inline values (.6rem, .72rem, .7rem) migrated — 240 sites.</t>
         </is>
       </c>
     </row>
@@ -3366,17 +3366,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Letter-spacing variants (0.02–0.32em)</t>
+          <t>Remaining font-size stragglers (.52, .55, .58, .65, .68, .8, .9rem etc)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Throughout</t>
+          <t>Throughout JSX inline styles</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>No system documented</t>
+          <t>Follow-up sweep — pattern established, just mechanical</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Line-height variants (1, 1.1, 1.15, 1.6, 1.65, 1.7)</t>
+          <t>Letter-spacing variants (0.02–0.32em)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3410,15 +3410,37 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Line-height variants (1, 1.1, 1.15, 1.6, 1.65, 1.7)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Throughout</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>No system documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>Font families: Cinzel, Cinzel Decorative, Inter, system-ui</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>src/styles/*.css</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mostly intentional but mixed by use case</t>
         </is>
@@ -3435,13 +3457,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="61" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3467,24 +3489,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>No spacing token system — hardcoded px throughout</t>
+          <t>Token system introduced (R + S scales)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>App.js inline styles</t>
+          <t>src/utils/tokens.js (new)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Adopt 4px-based scale (4,8,12,16,24,32)</t>
+          <t>Border-radius scale (sm→full) and 4px-based spacing scale (s2→s32). Top 3 borderRadius values (9, 8, 6) migrated — 89 sites.</t>
         </is>
       </c>
     </row>
@@ -3496,17 +3518,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>BorderRadius values 3,4,5,6,8,12,100</t>
+          <t>Remaining borderRadius stragglers (3,4,5,7,10,12,16)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Throughout</t>
+          <t>Throughout JSX inline styles</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Standardise to {4,6,8,9999}</t>
+          <t>Follow-up sweep — pattern established</t>
         </is>
       </c>
     </row>
@@ -3518,17 +3540,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mix of px-string and unitless React style values</t>
+          <t>Hardcoded gap/padding/margin px values</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Throughout</t>
+          <t>Throughout JSX inline styles</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Pick one convention</t>
+          <t>Migrate using tokens.S — follow-up sweep</t>
         </is>
       </c>
     </row>
@@ -3540,15 +3562,37 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Mix of px-string and unitless React style values</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Throughout</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Pick one convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>Negative margins for overlap (marginTop:-16, marginTop:-14)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>src/styles/landing.css:241,251</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Acceptable but document</t>
         </is>

--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -1108,7 +1108,7 @@
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>exercises.js:5012</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>alias (hidden from picker)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>exercises.js:19406</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>shown in picker</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>exercises.js:4921</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>alias (hidden from picker)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>exercises.js:19402</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>shown in picker</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>exercises.js:6975</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>alias (hidden from picker)</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>exercises.js:19414</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>shown in picker</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>exercises.js:16751</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>alias (hidden from picker)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>exercises.js:19458</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>shown in picker</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1729,19 +1729,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Dual-form catalog dedup</t>
+          <t>Dual-form catalog dedup via alias flag (no user-data migration needed)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>src/data/exercises.js + migration</t>
+          <t>src/data/exercises.js — 4 legacy entries marked alias:true; src/App.js splits picker (filtered) vs lookup (unfiltered)</t>
         </is>
       </c>
     </row>

--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -1521,7 +1521,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -1707,19 +1707,19 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Spacing/typography token system introduced + top values migrated</t>
+          <t>Spacing/typography token system — full sweep of font-size + borderRadius</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>src/utils/tokens.js (new) — 329 highest-frequency values migrated; remaining stragglers tracked</t>
+          <t>src/utils/tokens.js extended; 603 inline values migrated across App.js + PlanWizard.js</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="73" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Token system introduced (FS scale)</t>
+          <t>Token system introduced + full sweep</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>src/utils/tokens.js (new)</t>
+          <t>src/utils/tokens.js</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>8-step rem-based font-size scale (xxs→xxl). Top 3 inline values (.6rem, .72rem, .7rem) migrated — 240 sites.</t>
+          <t>FS scale extended to numeric (fs44–fs95) + semantic aliases (xxs–xxl). All 498 inline rem font-sizes across App.js + PlanWizard.js now reference tokens.</t>
         </is>
       </c>
     </row>
@@ -3366,17 +3366,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Remaining font-size stragglers (.52, .55, .58, .65, .68, .8, .9rem etc)</t>
+          <t>Letter-spacing variants (0.02–0.32em)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Throughout JSX inline styles</t>
+          <t>Throughout</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Follow-up sweep — pattern established, just mechanical</t>
+          <t>No system documented</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Letter-spacing variants (0.02–0.32em)</t>
+          <t>Line-height variants (1, 1.1, 1.15, 1.6, 1.65, 1.7)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3410,37 +3410,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Line-height variants (1, 1.1, 1.15, 1.6, 1.65, 1.7)</t>
+          <t>Font families: Cinzel, Cinzel Decorative, Inter, system-ui</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Throughout</t>
+          <t>src/styles/*.css</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>No system documented</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Font families: Cinzel, Cinzel Decorative, Inter, system-ui</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>src/styles/*.css</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Mostly intentional but mixed by use case</t>
         </is>
@@ -3496,39 +3474,39 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Token system introduced (R + S scales)</t>
+          <t>BorderRadius fully tokenised</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>src/utils/tokens.js (new)</t>
+          <t>src/utils/tokens.js R scale</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Border-radius scale (sm→full) and 4px-based spacing scale (s2→s32). Top 3 borderRadius values (9, 8, 6) migrated — 89 sites.</t>
+          <t>All 105 inline borderRadius values across App.js + PlanWizard.js now reference R.rN tokens (one per unique px value, plus semantic aliases).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Remaining borderRadius stragglers (3,4,5,7,10,12,16)</t>
+          <t>Spacing scale defined (S)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Throughout JSX inline styles</t>
+          <t>src/utils/tokens.js S scale</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Follow-up sweep — pattern established</t>
+          <t>19 numeric tokens covering 0–32 px values seen in the codebase. Migration of gap/padding/margin call-sites is a separate follow-up.</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3528,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Migrate using tokens.S — follow-up sweep</t>
+          <t>Migrate using tokens.S — needs scale-snapping policy first</t>
         </is>
       </c>
     </row>

--- a/Aurisar_Audit_Report.xlsx
+++ b/Aurisar_Audit_Report.xlsx
@@ -3435,12 +3435,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="61" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -3496,17 +3496,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spacing scale defined (S)</t>
+          <t>Spacing fully tokenised — Option B snap policy applied</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>src/utils/tokens.js S scale</t>
+          <t>src/utils/tokens.js S scale + App.js + PlanWizard.js</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>19 numeric tokens covering 0–32 px values seen in the codebase. Migration of gap/padding/margin call-sites is a separate follow-up.</t>
+          <t>1,119 inline gap/padding/margin sites migrated; 291 off-by-1 values snapped to nearest even (e.g. 5→6, 7→8); 828 pure renames. Final scale is even-step 0,2,4,…,32 plus negative overlap tokens.</t>
         </is>
       </c>
     </row>
@@ -3518,17 +3518,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Hardcoded gap/padding/margin px values</t>
+          <t>Mix of px-string and unitless React style values</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Throughout JSX inline styles</t>
+          <t>Throughout</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Migrate using tokens.S — needs scale-snapping policy first</t>
+          <t>Pick one convention</t>
         </is>
       </c>
     </row>
@@ -3540,37 +3540,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mix of px-string and unitless React style values</t>
+          <t>Negative margins for overlap (marginTop:-16, marginTop:-14)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Throughout</t>
+          <t>src/styles/landing.css:241,251</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Pick one convention</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Negative margins for overlap (marginTop:-16, marginTop:-14)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>src/styles/landing.css:241,251</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Acceptable but document</t>
         </is>
